--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92567031644</v>
+        <v>46157.93095947785</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93095947785</v>
+        <v>46157.93171302868</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93171302868</v>
+        <v>46157.93398858168</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93398858168</v>
+        <v>46157.93716603024</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93716603024</v>
+        <v>46158.28215223329</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28215223329</v>
+        <v>46158.29676728763</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29676728763</v>
+        <v>46158.29813302274</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29813302274</v>
+        <v>46158.33386165831</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33386165831</v>
+        <v>46158.3685594749</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.3685594749</v>
+        <v>46158.3728667005</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
